--- a/cet4/result/03_文学女王_从小编到主编/03_文学女王_从小编到主编_学习版.xlsx
+++ b/cet4/result/03_文学女王_从小编到主编/03_文学女王_从小编到主编_学习版.xlsx
@@ -397,1025 +397,773 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D72"/>
+  <dimension ref="A1:D54"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" customWidth="1"/>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
-    <col min="4" max="4" width="40.83203125" customWidth="1"/>
+    <col min="3" max="3" width="15.83203125" customWidth="1"/>
+    <col min="4" max="4" width="30.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>序号</v>
+        <v>词汇</v>
       </c>
       <c r="B1" t="str">
-        <v>单词</v>
+        <v>音标</v>
       </c>
       <c r="C1" t="str">
-        <v>中文释义</v>
+        <v>词性</v>
       </c>
       <c r="D1" t="str">
-        <v>完整形式</v>
+        <v>中文</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <v>1</v>
+      <c r="A2" t="str">
+        <v>editor</v>
       </c>
       <c r="B2" t="str">
-        <v>editor</v>
+        <v>/ˈedɪtər/</v>
       </c>
       <c r="C2" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D2" t="str">
         <v>编辑</v>
       </c>
-      <c r="D2" t="str">
-        <v>editor(编辑)📢</v>
-      </c>
     </row>
     <row r="3">
-      <c r="A3">
-        <v>2</v>
+      <c r="A3" t="str">
+        <v>beginning</v>
       </c>
       <c r="B3" t="str">
-        <v>beginning</v>
+        <v>/bɪˈɡɪnɪŋ/</v>
       </c>
       <c r="C3" t="str">
+        <v>n./v.</v>
+      </c>
+      <c r="D3" t="str">
         <v>开始</v>
       </c>
-      <c r="D3" t="str">
-        <v>beginning(开始)📢</v>
-      </c>
     </row>
     <row r="4">
-      <c r="A4">
-        <v>3</v>
+      <c r="A4" t="str">
+        <v>hard</v>
       </c>
       <c r="B4" t="str">
-        <v>hard</v>
+        <v>/hɑːrd/</v>
       </c>
       <c r="C4" t="str">
+        <v>v./adj./adv.</v>
+      </c>
+      <c r="D4" t="str">
         <v>困难的</v>
       </c>
-      <c r="D4" t="str">
-        <v>hard(困难的)📢</v>
-      </c>
     </row>
     <row r="5">
-      <c r="A5">
-        <v>4</v>
+      <c r="A5" t="str">
+        <v>doubtless</v>
       </c>
       <c r="B5" t="str">
-        <v>doubtless</v>
+        <v>/ˈdaʊtləs/</v>
       </c>
       <c r="C5" t="str">
+        <v>v./adj./adv.</v>
+      </c>
+      <c r="D5" t="str">
         <v>无疑地</v>
       </c>
-      <c r="D5" t="str">
-        <v>doubtless(无疑地)📢</v>
-      </c>
     </row>
     <row r="6">
-      <c r="A6">
-        <v>5</v>
+      <c r="A6" t="str">
+        <v>wood</v>
       </c>
       <c r="B6" t="str">
-        <v>wood</v>
+        <v>/wʊd/</v>
       </c>
       <c r="C6" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D6" t="str">
         <v>木材</v>
       </c>
-      <c r="D6" t="str">
-        <v>wood(木材)📢</v>
-      </c>
     </row>
     <row r="7">
-      <c r="A7">
-        <v>6</v>
+      <c r="A7" t="str">
+        <v>able</v>
       </c>
       <c r="B7" t="str">
-        <v>able</v>
+        <v>/ˈeɪbl/</v>
       </c>
       <c r="C7" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D7" t="str">
         <v>有能力的</v>
       </c>
-      <c r="D7" t="str">
-        <v>able(有能力的)📢</v>
-      </c>
     </row>
     <row r="8">
-      <c r="A8">
-        <v>7</v>
+      <c r="A8" t="str">
+        <v>introduce</v>
       </c>
       <c r="B8" t="str">
-        <v>introduce</v>
+        <v>/ˌɪntrəˈduːs/</v>
       </c>
       <c r="C8" t="str">
+        <v>vt.</v>
+      </c>
+      <c r="D8" t="str">
         <v>介绍</v>
       </c>
-      <c r="D8" t="str">
-        <v>introduce(介绍)📢</v>
-      </c>
     </row>
     <row r="9">
-      <c r="A9">
-        <v>8</v>
+      <c r="A9" t="str">
+        <v>entry</v>
       </c>
       <c r="B9" t="str">
-        <v>entry</v>
+        <v>/ˈentri/</v>
       </c>
       <c r="C9" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D9" t="str">
         <v>进入</v>
       </c>
-      <c r="D9" t="str">
-        <v>entry(进入)📢</v>
-      </c>
     </row>
     <row r="10">
-      <c r="A10">
-        <v>9</v>
+      <c r="A10" t="str">
+        <v>drawer</v>
       </c>
       <c r="B10" t="str">
-        <v>drawer</v>
+        <v>/drɔːr/</v>
       </c>
       <c r="C10" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D10" t="str">
         <v>抽屉</v>
       </c>
-      <c r="D10" t="str">
-        <v>drawer(抽屉)📢</v>
-      </c>
     </row>
     <row r="11">
-      <c r="A11">
-        <v>10</v>
+      <c r="A11" t="str">
+        <v>classroom</v>
       </c>
       <c r="B11" t="str">
-        <v>classroom</v>
+        <v>/ˈklɑːsruːm/</v>
       </c>
       <c r="C11" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D11" t="str">
         <v>教室</v>
       </c>
-      <c r="D11" t="str">
-        <v>classroom(教室)📢</v>
-      </c>
     </row>
     <row r="12">
-      <c r="A12">
-        <v>11</v>
+      <c r="A12" t="str">
+        <v>underline</v>
       </c>
       <c r="B12" t="str">
-        <v>underline</v>
+        <v>/ˌʌndərˈlaɪn/</v>
       </c>
       <c r="C12" t="str">
+        <v>n./vt.</v>
+      </c>
+      <c r="D12" t="str">
         <v>强调</v>
       </c>
-      <c r="D12" t="str">
-        <v>underline(强调)📢</v>
-      </c>
     </row>
     <row r="13">
-      <c r="A13">
-        <v>12</v>
+      <c r="A13" t="str">
+        <v>harm</v>
       </c>
       <c r="B13" t="str">
-        <v>harm</v>
+        <v>/hɑːrm/</v>
       </c>
       <c r="C13" t="str">
+        <v>n./vt.</v>
+      </c>
+      <c r="D13" t="str">
         <v>伤害</v>
       </c>
-      <c r="D13" t="str">
-        <v>harm(伤害)📢</v>
-      </c>
     </row>
     <row r="14">
-      <c r="A14">
-        <v>13</v>
+      <c r="A14" t="str">
+        <v>Except</v>
       </c>
       <c r="B14" t="str">
-        <v>Except</v>
+        <v/>
       </c>
       <c r="C14" t="str">
+        <v/>
+      </c>
+      <c r="D14" t="str">
         <v>除了</v>
       </c>
-      <c r="D14" t="str">
-        <v>Except(除了)📢</v>
-      </c>
     </row>
     <row r="15">
-      <c r="A15">
-        <v>14</v>
+      <c r="A15" t="str">
+        <v>religious</v>
       </c>
       <c r="B15" t="str">
-        <v>religious</v>
+        <v>/rɪˈlɪdʒəs/</v>
       </c>
       <c r="C15" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D15" t="str">
         <v>宗教的</v>
       </c>
-      <c r="D15" t="str">
-        <v>religious(宗教的)📢</v>
-      </c>
     </row>
     <row r="16">
-      <c r="A16">
-        <v>15</v>
+      <c r="A16" t="str">
+        <v>video</v>
       </c>
       <c r="B16" t="str">
-        <v>video</v>
+        <v>/ˈvɪdioʊ/</v>
       </c>
       <c r="C16" t="str">
+        <v>n./v./adj.</v>
+      </c>
+      <c r="D16" t="str">
         <v>视频</v>
       </c>
-      <c r="D16" t="str">
-        <v>video(视频)📢</v>
-      </c>
     </row>
     <row r="17">
-      <c r="A17">
-        <v>16</v>
+      <c r="A17" t="str">
+        <v>cafeteria</v>
       </c>
       <c r="B17" t="str">
-        <v>cafeteria</v>
+        <v>/ˌkæfəˈtɪriə/</v>
       </c>
       <c r="C17" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D17" t="str">
         <v>自助餐厅</v>
       </c>
-      <c r="D17" t="str">
-        <v>cafeteria(自助餐厅)📢</v>
-      </c>
     </row>
     <row r="18">
-      <c r="A18">
-        <v>17</v>
+      <c r="A18" t="str">
+        <v>bowl</v>
       </c>
       <c r="B18" t="str">
-        <v>bowl</v>
+        <v>/boʊl/</v>
       </c>
       <c r="C18" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D18" t="str">
         <v>碗</v>
       </c>
-      <c r="D18" t="str">
-        <v>bowl(碗)📢</v>
-      </c>
     </row>
     <row r="19">
-      <c r="A19">
-        <v>18</v>
+      <c r="A19" t="str">
+        <v>illness</v>
       </c>
       <c r="B19" t="str">
-        <v>illness</v>
+        <v>/ˈɪlnəs/</v>
       </c>
       <c r="C19" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D19" t="str">
         <v>疾病</v>
       </c>
-      <c r="D19" t="str">
-        <v>illness(疾病)📢</v>
-      </c>
     </row>
     <row r="20">
-      <c r="A20">
-        <v>19</v>
+      <c r="A20" t="str">
+        <v>proof</v>
       </c>
       <c r="B20" t="str">
-        <v>proof</v>
+        <v>/pruːf/</v>
       </c>
       <c r="C20" t="str">
+        <v>n./vt./adj.</v>
+      </c>
+      <c r="D20" t="str">
         <v>证明</v>
       </c>
-      <c r="D20" t="str">
-        <v>proof(证明)📢</v>
-      </c>
     </row>
     <row r="21">
-      <c r="A21">
-        <v>20</v>
+      <c r="A21" t="str">
+        <v>citizen</v>
       </c>
       <c r="B21" t="str">
-        <v>citizen</v>
+        <v>/ˈsɪtɪzn/</v>
       </c>
       <c r="C21" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D21" t="str">
         <v>公民</v>
       </c>
-      <c r="D21" t="str">
-        <v>citizen(公民)📢</v>
-      </c>
     </row>
     <row r="22">
-      <c r="A22">
-        <v>21</v>
+      <c r="A22" t="str">
+        <v>criticize</v>
       </c>
       <c r="B22" t="str">
-        <v>criticize</v>
+        <v>/ˈkrɪtɪsaɪz/</v>
       </c>
       <c r="C22" t="str">
+        <v>vt./vi.</v>
+      </c>
+      <c r="D22" t="str">
         <v>批评</v>
       </c>
-      <c r="D22" t="str">
-        <v>criticize(批评)📢</v>
-      </c>
     </row>
     <row r="23">
-      <c r="A23">
-        <v>22</v>
+      <c r="A23" t="str">
+        <v>intense</v>
       </c>
       <c r="B23" t="str">
-        <v>intense</v>
+        <v>/ɪnˈtens/</v>
       </c>
       <c r="C23" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D23" t="str">
         <v>强烈的</v>
       </c>
-      <c r="D23" t="str">
-        <v>intense(强烈的)📢</v>
-      </c>
     </row>
     <row r="24">
-      <c r="A24">
-        <v>23</v>
+      <c r="A24" t="str">
+        <v>weekday</v>
       </c>
       <c r="B24" t="str">
-        <v>weekday</v>
+        <v>/ˈwiːkdeɪ/</v>
       </c>
       <c r="C24" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D24" t="str">
         <v>工作日</v>
       </c>
-      <c r="D24" t="str">
-        <v>weekday(工作日)📢</v>
-      </c>
     </row>
     <row r="25">
-      <c r="A25">
-        <v>24</v>
+      <c r="A25" t="str">
+        <v>satisfactory</v>
       </c>
       <c r="B25" t="str">
-        <v>satisfactory</v>
+        <v>/ˌsætɪsˈfæktəri/</v>
       </c>
       <c r="C25" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D25" t="str">
         <v>满意的</v>
       </c>
-      <c r="D25" t="str">
-        <v>satisfactory(满意的)📢</v>
-      </c>
     </row>
     <row r="26">
-      <c r="A26">
-        <v>25</v>
+      <c r="A26" t="str">
+        <v>unpleasant</v>
       </c>
       <c r="B26" t="str">
-        <v>unpleasant</v>
+        <v>/ʌnˈpleznt/</v>
       </c>
       <c r="C26" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D26" t="str">
         <v>讨厌的</v>
       </c>
-      <c r="D26" t="str">
-        <v>unpleasant(讨厌的)📢</v>
-      </c>
     </row>
     <row r="27">
-      <c r="A27">
-        <v>26</v>
+      <c r="A27" t="str">
+        <v>bore</v>
       </c>
       <c r="B27" t="str">
-        <v>bore</v>
+        <v>/bɔːr/</v>
       </c>
       <c r="C27" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D27" t="str">
         <v>厌烦</v>
       </c>
-      <c r="D27" t="str">
-        <v>bore(厌烦)📢</v>
-      </c>
     </row>
     <row r="28">
-      <c r="A28">
-        <v>27</v>
+      <c r="A28" t="str">
+        <v>carbon</v>
       </c>
       <c r="B28" t="str">
-        <v>carbon</v>
+        <v>/ˈkɑːrbən/</v>
       </c>
       <c r="C28" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D28" t="str">
         <v>碳</v>
       </c>
-      <c r="D28" t="str">
-        <v>carbon(碳)📢</v>
-      </c>
     </row>
     <row r="29">
-      <c r="A29">
-        <v>28</v>
+      <c r="A29" t="str">
+        <v>different</v>
       </c>
       <c r="B29" t="str">
-        <v>different</v>
+        <v>/ˈdɪfrənt/</v>
       </c>
       <c r="C29" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D29" t="str">
         <v>不同的</v>
       </c>
-      <c r="D29" t="str">
-        <v>different(不同的)📢</v>
-      </c>
     </row>
     <row r="30">
-      <c r="A30">
-        <v>29</v>
+      <c r="A30" t="str">
+        <v>external</v>
       </c>
       <c r="B30" t="str">
-        <v>able</v>
+        <v>/ɪkˈstɜːrnl/</v>
       </c>
       <c r="C30" t="str">
-        <v>有能力的</v>
+        <v>n./adj.</v>
       </c>
       <c r="D30" t="str">
-        <v>able(有能力的)📢</v>
+        <v>外部的</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31">
-        <v>30</v>
+      <c r="A31" t="str">
+        <v>exceed</v>
       </c>
       <c r="B31" t="str">
-        <v>intense</v>
+        <v>/ɪkˈsiːd/</v>
       </c>
       <c r="C31" t="str">
-        <v>强烈的</v>
+        <v>vt./vi.</v>
       </c>
       <c r="D31" t="str">
-        <v>intense(强烈的)📢</v>
+        <v>超过</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32">
-        <v>31</v>
+      <c r="A32" t="str">
+        <v>unjust</v>
       </c>
       <c r="B32" t="str">
-        <v>carbon</v>
+        <v>/ˌʌnˈdʒʌst/</v>
       </c>
       <c r="C32" t="str">
-        <v>碳</v>
+        <v>adj.</v>
       </c>
       <c r="D32" t="str">
-        <v>carbon(碳)📢</v>
+        <v>不公平的</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33">
-        <v>32</v>
+      <c r="A33" t="str">
+        <v>phase</v>
       </c>
       <c r="B33" t="str">
-        <v>external</v>
+        <v>/feɪz/</v>
       </c>
       <c r="C33" t="str">
-        <v>外部的</v>
+        <v>n./vt.</v>
       </c>
       <c r="D33" t="str">
-        <v>external(外部的)📢</v>
+        <v>阶段</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34">
-        <v>33</v>
+      <c r="A34" t="str">
+        <v>successive</v>
       </c>
       <c r="B34" t="str">
-        <v>exceed</v>
+        <v>/səkˈsesɪv/</v>
       </c>
       <c r="C34" t="str">
-        <v>超过</v>
+        <v>adj.</v>
       </c>
       <c r="D34" t="str">
-        <v>exceed(超过)📢</v>
+        <v>连续的</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35">
-        <v>34</v>
+      <c r="A35" t="str">
+        <v>advice</v>
       </c>
       <c r="B35" t="str">
-        <v>unjust</v>
+        <v>/ədˈvaɪs/</v>
       </c>
       <c r="C35" t="str">
-        <v>不公平的</v>
+        <v>n.</v>
       </c>
       <c r="D35" t="str">
-        <v>unjust(不公平的)📢</v>
+        <v>建议</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36">
-        <v>35</v>
+      <c r="A36" t="str">
+        <v>visitor</v>
       </c>
       <c r="B36" t="str">
-        <v>phase</v>
+        <v>/ˈvɪzɪtər/</v>
       </c>
       <c r="C36" t="str">
-        <v>阶段</v>
+        <v>n.</v>
       </c>
       <c r="D36" t="str">
-        <v>phase(阶段)📢</v>
+        <v>访问者</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37">
-        <v>36</v>
+      <c r="A37" t="str">
+        <v>also</v>
       </c>
       <c r="B37" t="str">
-        <v>drawer</v>
+        <v>/ˈɔːlsoʊ/</v>
       </c>
       <c r="C37" t="str">
-        <v>抽屉</v>
+        <v>n./v./adv./conj.</v>
       </c>
       <c r="D37" t="str">
-        <v>drawer(抽屉)📢</v>
+        <v>也</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38">
-        <v>37</v>
+      <c r="A38" t="str">
+        <v>report</v>
       </c>
       <c r="B38" t="str">
-        <v>satisfactory</v>
+        <v>/rɪˈpɔːrt/</v>
       </c>
       <c r="C38" t="str">
-        <v>满意</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D38" t="str">
-        <v>satisfactory(满意)📢</v>
+        <v>报告</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39">
-        <v>38</v>
+      <c r="A39" t="str">
+        <v>in</v>
       </c>
       <c r="B39" t="str">
-        <v>successive</v>
+        <v>/ɪn/</v>
       </c>
       <c r="C39" t="str">
-        <v>连续的</v>
+        <v>n./v./adj./adv./prep.</v>
       </c>
       <c r="D39" t="str">
-        <v>successive(连续的)📢</v>
+        <v>在...里</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40">
-        <v>39</v>
+      <c r="A40" t="str">
+        <v>mute</v>
       </c>
       <c r="B40" t="str">
-        <v>unpleasant</v>
+        <v>/mjuːt/</v>
       </c>
       <c r="C40" t="str">
-        <v>讨厌的</v>
+        <v>n./vt./adj.</v>
       </c>
       <c r="D40" t="str">
-        <v>unpleasant(讨厌的)📢</v>
+        <v>哑的</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41">
-        <v>40</v>
+      <c r="A41" t="str">
+        <v>innocent</v>
       </c>
       <c r="B41" t="str">
-        <v>advice</v>
+        <v>/ˈɪnəsnt/</v>
       </c>
       <c r="C41" t="str">
-        <v>建议</v>
+        <v>n./adj.</v>
       </c>
       <c r="D41" t="str">
-        <v>advice(建议)📢</v>
+        <v>无辜的</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42">
-        <v>41</v>
+      <c r="A42" t="str">
+        <v>ugly</v>
       </c>
       <c r="B42" t="str">
-        <v>visitor</v>
+        <v>/ˈʌɡli/</v>
       </c>
       <c r="C42" t="str">
-        <v>访问者</v>
+        <v>adj.</v>
       </c>
       <c r="D42" t="str">
-        <v>visitor(访问者)📢</v>
+        <v>丑陋的</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43">
-        <v>42</v>
+      <c r="A43" t="str">
+        <v>decide</v>
       </c>
       <c r="B43" t="str">
-        <v>video</v>
+        <v>/dɪˈsaɪd/</v>
       </c>
       <c r="C43" t="str">
-        <v>视频</v>
+        <v>vt./vi.</v>
       </c>
       <c r="D43" t="str">
-        <v>video(视频)📢</v>
+        <v>决定</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44">
-        <v>43</v>
+      <c r="A44" t="str">
+        <v>cricket</v>
       </c>
       <c r="B44" t="str">
-        <v>also</v>
+        <v>/ˈkrɪkɪt/</v>
       </c>
       <c r="C44" t="str">
-        <v>也</v>
+        <v>n.</v>
       </c>
       <c r="D44" t="str">
-        <v>also(也)📢</v>
+        <v>蟋蟀</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45">
-        <v>44</v>
+      <c r="A45" t="str">
+        <v>grape</v>
       </c>
       <c r="B45" t="str">
-        <v>report</v>
+        <v>/ɡreɪp/</v>
       </c>
       <c r="C45" t="str">
-        <v>报告</v>
+        <v>n.</v>
       </c>
       <c r="D45" t="str">
-        <v>report(报告)📢</v>
+        <v>葡萄</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46">
-        <v>45</v>
+      <c r="A46" t="str">
+        <v>rent</v>
       </c>
       <c r="B46" t="str">
-        <v>in</v>
+        <v>/rent/</v>
       </c>
       <c r="C46" t="str">
-        <v>在...里</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D46" t="str">
-        <v>in(在...里)📢</v>
+        <v>租金</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47">
-        <v>46</v>
+      <c r="A47" t="str">
+        <v>puff</v>
       </c>
       <c r="B47" t="str">
-        <v>different</v>
+        <v>/pʌf/</v>
       </c>
       <c r="C47" t="str">
-        <v>不同的</v>
+        <v>n./v.</v>
       </c>
       <c r="D47" t="str">
-        <v>different(不同的)📢</v>
+        <v>喷</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48">
-        <v>47</v>
+      <c r="A48" t="str">
+        <v>contest</v>
       </c>
       <c r="B48" t="str">
-        <v>mute</v>
+        <v>/ˈkɑːntest/</v>
       </c>
       <c r="C48" t="str">
-        <v>哑的</v>
+        <v>n./v.</v>
       </c>
       <c r="D48" t="str">
-        <v>mute(哑的)📢</v>
+        <v>竞赛</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49">
-        <v>48</v>
+      <c r="A49" t="str">
+        <v>heel</v>
       </c>
       <c r="B49" t="str">
-        <v>innocent</v>
+        <v>/hiːl/</v>
       </c>
       <c r="C49" t="str">
-        <v>无辜的</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D49" t="str">
-        <v>innocent(无辜的)📢</v>
+        <v>脚后跟</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50">
-        <v>49</v>
+      <c r="A50" t="str">
+        <v>find</v>
       </c>
       <c r="B50" t="str">
-        <v>ugly</v>
+        <v>/faɪnd/</v>
       </c>
       <c r="C50" t="str">
-        <v>丑陋的</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D50" t="str">
-        <v>ugly(丑陋的)📢</v>
+        <v>找到</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51">
-        <v>50</v>
+      <c r="A51" t="str">
+        <v>mile</v>
       </c>
       <c r="B51" t="str">
-        <v>decide</v>
+        <v>/maɪl/</v>
       </c>
       <c r="C51" t="str">
-        <v>决定</v>
+        <v>n.</v>
       </c>
       <c r="D51" t="str">
-        <v>decide(决定)📢</v>
+        <v>英里</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52">
-        <v>51</v>
+      <c r="A52" t="str">
+        <v>nevertheless</v>
       </c>
       <c r="B52" t="str">
-        <v>cricket</v>
+        <v>/ˌnevərðəˈles/</v>
       </c>
       <c r="C52" t="str">
-        <v>蟋蟀</v>
+        <v>v./adv.</v>
       </c>
       <c r="D52" t="str">
-        <v>cricket(蟋蟀)📢</v>
+        <v>然而</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53">
-        <v>52</v>
+      <c r="A53" t="str">
+        <v>thank</v>
       </c>
       <c r="B53" t="str">
-        <v>grape</v>
+        <v>/θæŋk/</v>
       </c>
       <c r="C53" t="str">
-        <v>葡萄</v>
+        <v>n./vt./int.</v>
       </c>
       <c r="D53" t="str">
-        <v>grape(葡萄)📢</v>
+        <v>感谢</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54">
-        <v>53</v>
+      <c r="A54" t="str">
+        <v>for</v>
       </c>
       <c r="B54" t="str">
-        <v>phase</v>
+        <v>/fər,fɔːr/</v>
       </c>
       <c r="C54" t="str">
-        <v>阶段</v>
+        <v>prep./conj.</v>
       </c>
       <c r="D54" t="str">
-        <v>phase(阶段)📢</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55">
-        <v>54</v>
-      </c>
-      <c r="B55" t="str">
-        <v>rent</v>
-      </c>
-      <c r="C55" t="str">
-        <v>租金</v>
-      </c>
-      <c r="D55" t="str">
-        <v>rent(租金)📢</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56">
-        <v>55</v>
-      </c>
-      <c r="B56" t="str">
-        <v>puff</v>
-      </c>
-      <c r="C56" t="str">
-        <v>喷</v>
-      </c>
-      <c r="D56" t="str">
-        <v>puff(喷)📢</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57">
-        <v>56</v>
-      </c>
-      <c r="B57" t="str">
-        <v>contest</v>
-      </c>
-      <c r="C57" t="str">
-        <v>竞赛</v>
-      </c>
-      <c r="D57" t="str">
-        <v>contest(竞赛)📢</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58">
-        <v>57</v>
-      </c>
-      <c r="B58" t="str">
-        <v>illness</v>
-      </c>
-      <c r="C58" t="str">
-        <v>生病</v>
-      </c>
-      <c r="D58" t="str">
-        <v>illness(生病)📢</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59">
-        <v>58</v>
-      </c>
-      <c r="B59" t="str">
-        <v>heel</v>
-      </c>
-      <c r="C59" t="str">
-        <v>脚后跟</v>
-      </c>
-      <c r="D59" t="str">
-        <v>heel(脚后跟)📢</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60">
-        <v>59</v>
-      </c>
-      <c r="B60" t="str">
-        <v>grape</v>
-      </c>
-      <c r="C60" t="str">
-        <v>葡萄</v>
-      </c>
-      <c r="D60" t="str">
-        <v>grape(葡萄)📢</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61">
-        <v>60</v>
-      </c>
-      <c r="B61" t="str">
-        <v>find</v>
-      </c>
-      <c r="C61" t="str">
-        <v>找到</v>
-      </c>
-      <c r="D61" t="str">
-        <v>find(找到)📢</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62">
-        <v>61</v>
-      </c>
-      <c r="B62" t="str">
-        <v>grape</v>
-      </c>
-      <c r="C62" t="str">
-        <v>葡萄</v>
-      </c>
-      <c r="D62" t="str">
-        <v>grape(葡萄)📢</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63">
-        <v>62</v>
-      </c>
-      <c r="B63" t="str">
-        <v>mile</v>
-      </c>
-      <c r="C63" t="str">
-        <v>英里</v>
-      </c>
-      <c r="D63" t="str">
-        <v>mile(英里)📢</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64">
-        <v>63</v>
-      </c>
-      <c r="B64" t="str">
-        <v>beginning</v>
-      </c>
-      <c r="C64" t="str">
-        <v>开始</v>
-      </c>
-      <c r="D64" t="str">
-        <v>beginning(开始)📢</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65">
-        <v>64</v>
-      </c>
-      <c r="B65" t="str">
-        <v>nevertheless</v>
-      </c>
-      <c r="C65" t="str">
-        <v>然而</v>
-      </c>
-      <c r="D65" t="str">
-        <v>nevertheless(然而)📢</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66">
-        <v>65</v>
-      </c>
-      <c r="B66" t="str">
-        <v>satisfactory</v>
-      </c>
-      <c r="C66" t="str">
-        <v>满意的</v>
-      </c>
-      <c r="D66" t="str">
-        <v>satisfactory(满意的)📢</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67">
-        <v>66</v>
-      </c>
-      <c r="B67" t="str">
-        <v>weekday</v>
-      </c>
-      <c r="C67" t="str">
-        <v>工作日</v>
-      </c>
-      <c r="D67" t="str">
-        <v>weekday(工作日)📢</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68">
-        <v>67</v>
-      </c>
-      <c r="B68" t="str">
-        <v>thank</v>
-      </c>
-      <c r="C68" t="str">
-        <v>感谢</v>
-      </c>
-      <c r="D68" t="str">
-        <v>thank(感谢)📢</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69">
-        <v>68</v>
-      </c>
-      <c r="B69" t="str">
-        <v>also</v>
-      </c>
-      <c r="C69" t="str">
-        <v>也</v>
-      </c>
-      <c r="D69" t="str">
-        <v>also(也)📢</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70">
-        <v>69</v>
-      </c>
-      <c r="B70" t="str">
-        <v>cricket</v>
-      </c>
-      <c r="C70" t="str">
-        <v>蟋蟀</v>
-      </c>
-      <c r="D70" t="str">
-        <v>cricket(蟋蟀)📢</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71">
-        <v>70</v>
-      </c>
-      <c r="B71" t="str">
-        <v>grape</v>
-      </c>
-      <c r="C71" t="str">
-        <v>葡萄</v>
-      </c>
-      <c r="D71" t="str">
-        <v>grape(葡萄)📢</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72">
-        <v>71</v>
-      </c>
-      <c r="B72" t="str">
-        <v>for</v>
-      </c>
-      <c r="C72" t="str">
         <v>为了</v>
-      </c>
-      <c r="D72" t="str">
-        <v>for(为了)📢</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D72"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D54"/>
   </ignoredErrors>
 </worksheet>
 </file>